--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -11,12 +11,13 @@
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
     <sheet name="Include #3" r:id="rId7" sheetId="5"/>
+    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,6 +125,9 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/terminologie-medicabase</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/terminologie-nuva/</t>
   </si>
 </sst>
 </file>
@@ -543,4 +547,44 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-medication-translation-document.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
